--- a/tests/fixtures/dic2.xlsx
+++ b/tests/fixtures/dic2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05167B6-8DEA-4A3B-B9D6-03AFFA6968BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDDB161-CD79-48FD-93ED-BF6EFB38B444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
   <si>
     <t>name</t>
   </si>
@@ -58,12 +58,6 @@
     <t>level_id</t>
   </si>
   <si>
-    <t>left_id</t>
-  </si>
-  <si>
-    <t>right_id</t>
-  </si>
-  <si>
     <t>gl_no</t>
   </si>
   <si>
@@ -92,6 +86,9 @@
   </si>
   <si>
     <t>dupl</t>
+  </si>
+  <si>
+    <t>amt_fin</t>
   </si>
 </sst>
 </file>
@@ -188,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -196,8 +193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,19 +520,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -554,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -583,14 +579,13 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="b">
         <f>FALSE()</f>
@@ -605,13 +600,12 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -639,11 +633,10 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -652,11 +645,10 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>0</v>
@@ -668,7 +660,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -680,10 +672,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
       </c>
       <c r="C12" t="b">
         <f>FALSE()</f>
@@ -692,10 +684,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
       </c>
       <c r="C13" t="b">
         <f>FALSE()</f>
@@ -704,7 +696,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -716,7 +708,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -728,10 +720,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
+        <v>19</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="C16" t="b">
         <f>FALSE()</f>
@@ -740,10 +732,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C17" t="b">
         <f>FALSE()</f>
@@ -752,10 +744,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
       </c>
       <c r="C18" t="b">
         <f>FALSE()</f>
